--- a/territory.xlsx
+++ b/territory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2815F89-FBA6-4198-8E78-DDA55D2B01B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC0A1C5-E6B4-49A7-A8A5-0D6A45D6807F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="3" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15200" windowHeight="6930" activeTab="4" xr2:uid="{B141029A-C238-484B-8693-F95FDEE8D83E}"/>
   </bookViews>
   <sheets>
     <sheet name="mun" sheetId="3" r:id="rId1"/>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
